--- a/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
+++ b/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Result</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:44:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:44:48 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -512,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -529,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>

--- a/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
+++ b/KatalonData/RADTestData/MFLNLessThanFiveError.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Result</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:17:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:17:19 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -512,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -529,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
